--- a/artfynd/A 33332-2025 artfynd.xlsx
+++ b/artfynd/A 33332-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379803</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126379920</v>
       </c>
       <c r="B3" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33332-2025 artfynd.xlsx
+++ b/artfynd/A 33332-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126379803</v>
+        <v>126379920</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -710,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näsberg, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529481</v>
+        <v>529364</v>
       </c>
       <c r="R2" t="n">
-        <v>6846768</v>
+        <v>6846108</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379920</v>
+        <v>126379801</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -816,14 +816,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Näsberg, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529364</v>
+        <v>529361</v>
       </c>
       <c r="R3" t="n">
-        <v>6846108</v>
+        <v>6846806</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -884,6 +884,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126379803</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Näsberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>529481</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6846768</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33332-2025 artfynd.xlsx
+++ b/artfynd/A 33332-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379920</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379801</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379803</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>